--- a/ig/DM-SEPTEMBRE-2026/CodeSystem-TRE-R211-ActiviteOperationnelle.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/CodeSystem-TRE-R211-ActiviteOperationnelle.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2193" uniqueCount="1528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2194" uniqueCount="1529">
   <si>
     <t>Property</t>
   </si>
@@ -4528,7 +4528,10 @@
     <t>625</t>
   </si>
   <si>
-    <t>Orthoptie : orientation troubles neuro-visuels (pathologies neurologiques, maladies neurodégénératives)</t>
+    <t>Orthoptie orientation neurovisuelle adulte (pathologies neurologiques, maladies neurodégénératives)</t>
+  </si>
+  <si>
+    <t>Activité orthoptique dédiée au repérage, à l'évaluation et à la prise en soins des troubles neurovisuels de l'adulte consécutifs à une atteinte neurologique acquise, neuro-ophtalmologique, neurodégénérative ou une lésion cérébrale acquise : troubles oculomoteurs, altérations du champ visuel d'origine neurologique, hémianopsie, négligence spatiale unilatérale, troubles de la cognition visuelle.  Cette activité contribue au diagnostic fonctionnel, à l'élaboration du projet de soins, à la prise en soins neurovisuelle, au suivi de l'évolution et à l'évaluation de l'efficacité des prises en soins.</t>
   </si>
   <si>
     <t>626</t>
@@ -12960,20 +12963,22 @@
       <c r="C626" t="s" s="2">
         <v>1504</v>
       </c>
-      <c r="D626" s="2"/>
+      <c r="D626" t="s" s="2">
+        <v>1505</v>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="s" s="2">
         <v>61</v>
       </c>
       <c r="B627" t="s" s="2">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="C627" t="s" s="2">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="D627" t="s" s="2">
-        <v>1507</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="628">
@@ -12981,13 +12986,13 @@
         <v>61</v>
       </c>
       <c r="B628" t="s" s="2">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="C628" t="s" s="2">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="D628" t="s" s="2">
-        <v>1510</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="629">
@@ -12995,10 +13000,10 @@
         <v>61</v>
       </c>
       <c r="B629" t="s" s="2">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="C629" t="s" s="2">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="D629" s="2"/>
     </row>
@@ -13007,10 +13012,10 @@
         <v>61</v>
       </c>
       <c r="B630" t="s" s="2">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="C630" t="s" s="2">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="D630" s="2"/>
     </row>
@@ -13019,10 +13024,10 @@
         <v>61</v>
       </c>
       <c r="B631" t="s" s="2">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="C631" t="s" s="2">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="D631" s="2"/>
     </row>
@@ -13031,10 +13036,10 @@
         <v>61</v>
       </c>
       <c r="B632" t="s" s="2">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="C632" t="s" s="2">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="D632" s="2"/>
     </row>
@@ -13043,10 +13048,10 @@
         <v>61</v>
       </c>
       <c r="B633" t="s" s="2">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="C633" t="s" s="2">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="D633" s="2"/>
     </row>
@@ -13055,10 +13060,10 @@
         <v>61</v>
       </c>
       <c r="B634" t="s" s="2">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="C634" t="s" s="2">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="D634" s="2"/>
     </row>
@@ -13067,13 +13072,13 @@
         <v>61</v>
       </c>
       <c r="B635" t="s" s="2">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="C635" t="s" s="2">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="D635" t="s" s="2">
-        <v>1525</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="636">
@@ -13084,10 +13089,10 @@
         <v>34</v>
       </c>
       <c r="C636" t="s" s="2">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="D636" t="s" s="2">
-        <v>1527</v>
+        <v>1528</v>
       </c>
     </row>
   </sheetData>
